--- a/Mapas/Excels/Nodes_ENTSOE.xlsx
+++ b/Mapas/Excels/Nodes_ENTSOE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0B688E1-1BA1-4C0E-8098-D65CF7111CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8F97EF-47D5-4893-B1F3-08A8A6A1BD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3ECAB5B8-515A-4E5B-A53D-CF71BE525F88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="550">
   <si>
     <t>ALDEADAVILA II</t>
   </si>
@@ -1187,13 +1187,505 @@
     <t>SERALLO</t>
   </si>
   <si>
-    <t>CIUDAD RODRIGO</t>
-  </si>
-  <si>
     <t>OBJECTID</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>ELCOGAS</t>
+  </si>
+  <si>
+    <t>MURTERAR</t>
+  </si>
+  <si>
+    <t>ACECA</t>
+  </si>
+  <si>
+    <t>ANDUJAR</t>
+  </si>
+  <si>
+    <t>CASILLAS</t>
+  </si>
+  <si>
+    <t>VILLANUEVA DEL REY</t>
+  </si>
+  <si>
+    <t>LA MANCHA</t>
+  </si>
+  <si>
+    <t>MONTECILLO BAJO</t>
+  </si>
+  <si>
+    <t>ARROYO DEL VALLE</t>
+  </si>
+  <si>
+    <t>AZUTAN</t>
+  </si>
+  <si>
+    <t>CIUDAD REAL</t>
+  </si>
+  <si>
+    <t>LA SOLANA</t>
+  </si>
+  <si>
+    <t>GUADAME</t>
+  </si>
+  <si>
+    <t>VENTA DE LA INES</t>
+  </si>
+  <si>
+    <t>PUERTOLLANO</t>
+  </si>
+  <si>
+    <t>PICON</t>
+  </si>
+  <si>
+    <t>ALARCOS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>EL EMPERADOR</t>
+  </si>
+  <si>
+    <t>MEDINA DEL CAMPO</t>
+  </si>
+  <si>
+    <t>OTERO DE HERREROS</t>
+  </si>
+  <si>
+    <t>LASTRAS DEL POZO</t>
+  </si>
+  <si>
+    <t>GALAPAGAR</t>
+  </si>
+  <si>
+    <t>VALLADOLID</t>
+  </si>
+  <si>
+    <t>ZARATAN</t>
+  </si>
+  <si>
+    <t>TORDESILLAS</t>
+  </si>
+  <si>
+    <t>MUDARRITA</t>
+  </si>
+  <si>
+    <t>LA MUDARRA</t>
+  </si>
+  <si>
+    <t>RENEDO</t>
+  </si>
+  <si>
+    <t>MADRIDEJOS</t>
+  </si>
+  <si>
+    <t>LA PALOMA</t>
+  </si>
+  <si>
+    <t>MORATA</t>
+  </si>
+  <si>
+    <t>HUELVES</t>
+  </si>
+  <si>
+    <t>JOSE CABRERA</t>
+  </si>
+  <si>
+    <t>TRILLO</t>
+  </si>
+  <si>
+    <t>ELEREBRO</t>
+  </si>
+  <si>
+    <t>TAFALLA</t>
+  </si>
+  <si>
+    <t>QUEL</t>
+  </si>
+  <si>
+    <t>ORCOYEN</t>
+  </si>
+  <si>
+    <t>CORDOVILLA</t>
+  </si>
+  <si>
+    <t>ELGEA</t>
+  </si>
+  <si>
+    <t>ARKALE</t>
+  </si>
+  <si>
+    <t>VALLDURGENT</t>
+  </si>
+  <si>
+    <t>SAN ORLANDIS</t>
+  </si>
+  <si>
+    <t>SON REUS</t>
+  </si>
+  <si>
+    <t>ES BESSONS</t>
+  </si>
+  <si>
+    <t>LLUBI</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>MONCAYO</t>
+  </si>
+  <si>
+    <t>ONCALA</t>
+  </si>
+  <si>
+    <t>CABRA</t>
+  </si>
+  <si>
+    <t>MURUARTE</t>
+  </si>
+  <si>
+    <t>CASTEJON</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CIUDADELA</t>
+  </si>
+  <si>
+    <t>ALGETE</t>
+  </si>
+  <si>
+    <t>TRES CANTOS</t>
+  </si>
+  <si>
+    <t>LA CEREAL</t>
+  </si>
+  <si>
+    <t>MECO</t>
+  </si>
+  <si>
+    <t>AENA</t>
+  </si>
+  <si>
+    <t>LOECHES</t>
+  </si>
+  <si>
+    <t>VILLAVERDE</t>
+  </si>
+  <si>
+    <t>FUENCARRAL</t>
+  </si>
+  <si>
+    <t>ARROYO DE LA VEGA</t>
+  </si>
+  <si>
+    <t>PTE.SAN FERNANDO</t>
+  </si>
+  <si>
+    <t>NUEVA ARDOZ</t>
+  </si>
+  <si>
+    <t>E.T.MAJADAHONDA</t>
+  </si>
+  <si>
+    <t>ARAVACA</t>
+  </si>
+  <si>
+    <t>BOADILLA</t>
+  </si>
+  <si>
+    <t>VILLAVICIOSA</t>
+  </si>
+  <si>
+    <t>MORALEJA</t>
+  </si>
+  <si>
+    <t>CASA CAMPO</t>
+  </si>
+  <si>
+    <t>COSLADA</t>
+  </si>
+  <si>
+    <t>SANTA ENGRACIA</t>
+  </si>
+  <si>
+    <t>ARRUBAL</t>
+  </si>
+  <si>
+    <t>OLITE</t>
+  </si>
+  <si>
+    <t>SANTA PONSA</t>
+  </si>
+  <si>
+    <t>BRAZATORTAS</t>
+  </si>
+  <si>
+    <t>VALDEMORO</t>
+  </si>
+  <si>
+    <t>FUENTES DE LA ALCARRIA</t>
+  </si>
+  <si>
+    <t>LA RODA DE ANDALUCIA</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>SEGOVIA</t>
+  </si>
+  <si>
+    <t>ALCARAMA</t>
+  </si>
+  <si>
+    <t>DAGANZO</t>
+  </si>
+  <si>
+    <t>ALMODOVAR</t>
+  </si>
+  <si>
+    <t>MANZANARES</t>
+  </si>
+  <si>
+    <t>HERNANI</t>
+  </si>
+  <si>
+    <t>IRUN</t>
+  </si>
+  <si>
+    <t>CARMONA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA ESCUDEROS</t>
+  </si>
+  <si>
+    <t>LAS ARROYADAS</t>
+  </si>
+  <si>
+    <t>CAS TRESORER</t>
+  </si>
+  <si>
+    <t>PASAJES</t>
+  </si>
+  <si>
+    <t>CARROYUELAS</t>
+  </si>
+  <si>
+    <t>LA NAVA</t>
+  </si>
+  <si>
+    <t>MAGAÑA</t>
+  </si>
+  <si>
+    <t>ORMAEZTEGUI</t>
+  </si>
+  <si>
+    <t>ARISTRAIN</t>
+  </si>
+  <si>
+    <t>LANZAS AGUDAS</t>
+  </si>
+  <si>
+    <t>TREVAGO</t>
+  </si>
+  <si>
+    <t>LA TORRECILLA</t>
+  </si>
+  <si>
+    <t>E.T.</t>
+  </si>
+  <si>
+    <t>VALLECAS</t>
+  </si>
+  <si>
+    <t>E.T.FUENCARRAL</t>
+  </si>
+  <si>
+    <t>MAJADAHONDA</t>
+  </si>
+  <si>
+    <t>VALLE DEL ARCIPRESTE</t>
+  </si>
+  <si>
+    <t>PRADO SANTO</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>LA FORTUNA</t>
+  </si>
+  <si>
+    <t>CAMINO FREGACEDOS</t>
+  </si>
+  <si>
+    <t>LEGANES</t>
+  </si>
+  <si>
+    <t>FUENLABRADA</t>
+  </si>
+  <si>
+    <t>BUENAVISTA</t>
+  </si>
+  <si>
+    <t>PARQUE INGENIEROS</t>
+  </si>
+  <si>
+    <t>AGUACATE</t>
+  </si>
+  <si>
+    <t>ANTONIO LEYVA</t>
+  </si>
+  <si>
+    <t>POLIGONO C</t>
+  </si>
+  <si>
+    <t>VENTAS DEL BATAN</t>
+  </si>
+  <si>
+    <t>NORTE</t>
+  </si>
+  <si>
+    <t>AZCA</t>
+  </si>
+  <si>
+    <t>HORTALEZA</t>
+  </si>
+  <si>
+    <t>SANCHINARRO</t>
+  </si>
+  <si>
+    <t>MIRASIERRA</t>
+  </si>
+  <si>
+    <t>GETAFE</t>
+  </si>
+  <si>
+    <t>RETAMAR</t>
+  </si>
+  <si>
+    <t>CANILLEJAS</t>
+  </si>
+  <si>
+    <t>SIMANCAS</t>
+  </si>
+  <si>
+    <t>CAMPO DE LAS NACIONES</t>
+  </si>
+  <si>
+    <t>COTO</t>
+  </si>
+  <si>
+    <t>PROSPERIDAD</t>
+  </si>
+  <si>
+    <t>MANUEL BECERRA</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>MAZARREDO</t>
+  </si>
+  <si>
+    <t>MELANCOLICOS</t>
+  </si>
+  <si>
+    <t>ARGANZUELA</t>
+  </si>
+  <si>
+    <t>PUENTE PRINCESA</t>
+  </si>
+  <si>
+    <t>CERRO PLATA</t>
+  </si>
+  <si>
+    <t>ARENAS DE SAN JUAN</t>
+  </si>
+  <si>
+    <t>ARGANDA</t>
+  </si>
+  <si>
+    <t>EL PILAR</t>
+  </si>
+  <si>
+    <t>CIUDAD DEPORTIVA</t>
+  </si>
+  <si>
+    <t>HORNILLO</t>
+  </si>
+  <si>
+    <t>PINTO AYUDEN</t>
+  </si>
+  <si>
+    <t>PINTO</t>
+  </si>
+  <si>
+    <t>PARLA</t>
+  </si>
+  <si>
+    <t>TALAVERA</t>
+  </si>
+  <si>
+    <t>TORRIJOS</t>
+  </si>
+  <si>
+    <t>EBORA</t>
+  </si>
+  <si>
+    <t>LOS PRADILLOS</t>
+  </si>
+  <si>
+    <t>ANOVER</t>
+  </si>
+  <si>
+    <t>VILLARES DEL SAZ</t>
+  </si>
+  <si>
+    <t>BELINCHON</t>
+  </si>
+  <si>
+    <t>ANCHUELO</t>
+  </si>
+  <si>
+    <t>BOLARQUE II</t>
+  </si>
+  <si>
+    <t>EL LLANO</t>
+  </si>
+  <si>
+    <t>TORRENT</t>
+  </si>
+  <si>
+    <t>FORMENTERA</t>
+  </si>
+  <si>
+    <t>IBIZA</t>
+  </si>
+  <si>
+    <t>MERCADAL</t>
+  </si>
+  <si>
+    <t>MAHON</t>
+  </si>
+  <si>
+    <t>DRAGONERA</t>
+  </si>
+  <si>
+    <t>ALCOBENDAS</t>
+  </si>
+  <si>
+    <t>VALDECARRETAS</t>
   </si>
 </sst>
 </file>
@@ -1588,3095 +2080,4977 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4927EC98-8F88-4518-B5E4-B3E0FF457BCE}">
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B664"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>3819</v>
+      </c>
+      <c r="B2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>3837</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3876</v>
+      </c>
+      <c r="B13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>3892</v>
+      </c>
+      <c r="B20" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>3893</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B21" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>3896</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B24" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>3897</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B25" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>3898</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>3899</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>3901</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B29" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>3902</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B30" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>3903</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>3905</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>3906</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B34" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>3907</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>3908</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B36" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>3909</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B37" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>3910</v>
+      </c>
+      <c r="B38" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>3911</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B39" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>3912</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>3914</v>
+      </c>
+      <c r="B42" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>3915</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B43" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44">
         <v>3916</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3917</v>
+      </c>
+      <c r="B45" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
         <v>3918</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3919</v>
+      </c>
+      <c r="B47" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3920</v>
+      </c>
+      <c r="B48" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
         <v>3921</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B49" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
         <v>3922</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B50" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
         <v>3923</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B51" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
         <v>3924</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B52" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53">
         <v>3925</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B53" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3926</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3927</v>
+      </c>
+      <c r="B55" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56">
         <v>3928</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B56" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57">
         <v>3929</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B57" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58">
         <v>3930</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B58" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59">
         <v>3931</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B59" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>3932</v>
+      </c>
+      <c r="B60" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61">
         <v>3933</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B61" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>3934</v>
+      </c>
+      <c r="B62" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>3935</v>
+      </c>
+      <c r="B63" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>3936</v>
+      </c>
+      <c r="B64" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>3937</v>
+      </c>
+      <c r="B65" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>3938</v>
+      </c>
+      <c r="B66" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>3939</v>
+      </c>
+      <c r="B67" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>3940</v>
+      </c>
+      <c r="B68" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>3941</v>
+      </c>
+      <c r="B69" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>3942</v>
+      </c>
+      <c r="B70" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
         <v>3943</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B71" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72">
         <v>3944</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B72" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73">
         <v>3945</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B73" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74">
         <v>3946</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B74" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75">
         <v>3947</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B75" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76">
         <v>3948</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B76" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77">
         <v>3950</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B77" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78">
         <v>3951</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B78" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79">
         <v>3952</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B79" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80">
         <v>3953</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B80" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81">
         <v>3954</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B81" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82">
         <v>3955</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B82" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83">
         <v>3956</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B83" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84">
         <v>3957</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B84" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85">
         <v>3958</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B85" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86">
         <v>3959</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B86" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87">
         <v>3960</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B87" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88">
         <v>3961</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B88" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89">
         <v>3962</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B89" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90">
         <v>3963</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B90" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91">
         <v>3964</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B91" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93">
         <v>3966</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B93" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94">
         <v>3967</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B94" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95">
         <v>3968</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B95" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96">
         <v>3969</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B96" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97">
         <v>3970</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B97" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98">
         <v>3971</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B98" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99">
         <v>3972</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B99" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100">
         <v>3973</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B100" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101">
         <v>3974</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B101" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>3975</v>
+      </c>
+      <c r="B102" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>3976</v>
+      </c>
+      <c r="B103" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>3977</v>
+      </c>
+      <c r="B104" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>3978</v>
+      </c>
+      <c r="B105" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>3979</v>
+      </c>
+      <c r="B106" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>3980</v>
+      </c>
+      <c r="B107" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>3981</v>
+      </c>
+      <c r="B108" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>3982</v>
+      </c>
+      <c r="B109" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>3983</v>
+      </c>
+      <c r="B110" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>3984</v>
+      </c>
+      <c r="B111" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112">
         <v>3985</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B112" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113">
         <v>3986</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B113" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114">
         <v>3987</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B114" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115">
         <v>3988</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B115" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116">
         <v>3989</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B116" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117">
         <v>3990</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B117" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119">
         <v>3992</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B119" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120">
         <v>3993</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B120" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121">
         <v>3994</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B121" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="1">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123">
         <v>3996</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B123" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="1">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124">
         <v>3997</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B124" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="1">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126">
         <v>3999</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B126" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="1">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127">
         <v>4000</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B127" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="1">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128">
         <v>4001</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B128" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="1">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129">
         <v>4002</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B129" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="1">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130">
         <v>4003</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B130" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="1">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131">
         <v>4004</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B131" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="1">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132">
         <v>4005</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B132" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="1">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133">
         <v>4006</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B133" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="1">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134">
         <v>4007</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B134" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="1">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136">
         <v>4009</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B136" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="1">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137">
         <v>4010</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B137" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="1">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138">
         <v>4011</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B138" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="1">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140">
         <v>4013</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B140" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="1">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141">
         <v>4014</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B141" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="1">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142">
         <v>4015</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B142" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="1">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143">
         <v>4016</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B143" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="1">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>4017</v>
+      </c>
+      <c r="B144" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>4018</v>
+      </c>
+      <c r="B145" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>4019</v>
+      </c>
+      <c r="B146" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>4021</v>
+      </c>
+      <c r="B148" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149">
         <v>4022</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B149" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="1">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150">
         <v>4023</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B150" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="1">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>4024</v>
+      </c>
+      <c r="B151" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>4025</v>
+      </c>
+      <c r="B152" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153">
         <v>4026</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B153" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="1">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154">
         <v>4027</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B154" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="1">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155">
         <v>4028</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B155" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="1">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156">
         <v>4029</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B156" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="1">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157">
         <v>4030</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B157" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="1">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159">
         <v>4032</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B159" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="1">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160">
         <v>4033</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B160" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="1">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161">
         <v>4034</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B161" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="1">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162">
         <v>4035</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B162" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="1">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163">
         <v>4036</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B163" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="1">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164">
         <v>4037</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B164" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="1">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165">
         <v>4038</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B165" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="1">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166">
         <v>4039</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B166" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="1">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A167">
         <v>4040</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B167" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="1">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A169">
         <v>4042</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B169" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="1">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A170">
         <v>4043</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B170" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="1">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A171">
         <v>4044</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B171" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="1">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A172">
         <v>4045</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B172" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="1">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A173">
         <v>4046</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B173" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="1">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A174">
         <v>4047</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B174" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="1">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A175">
         <v>4048</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B175" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="1">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A176">
         <v>4049</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B176" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="1">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A177">
         <v>4050</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B177" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="1">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A178">
         <v>4051</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B178" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="1">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A180">
         <v>4053</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B180" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="1">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A182">
         <v>4055</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B182" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="1">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A183">
         <v>4056</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B183" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="1">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A184">
         <v>4057</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B184" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="1">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A185">
         <v>4058</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B185" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="1">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>4059</v>
+      </c>
+      <c r="B186" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A187">
         <v>4060</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B187" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="1">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A188">
         <v>4061</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B188" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="1">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A190">
         <v>4063</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B190" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="1">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>4064</v>
+      </c>
+      <c r="B191" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>4065</v>
+      </c>
+      <c r="B192" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>4067</v>
+      </c>
+      <c r="B194" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>4068</v>
+      </c>
+      <c r="B195" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A196">
         <v>4069</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B196" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="1">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A197">
         <v>4070</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B197" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="1">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A198">
         <v>4071</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B198" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" s="1">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A199">
         <v>4072</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B199" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="1">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A200">
         <v>4073</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B200" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="1">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A201">
         <v>4074</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B201" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" s="1">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A202">
         <v>4075</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B202" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="1">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A203">
         <v>4076</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B203" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="1">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A204">
         <v>4077</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B204" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="1">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A205">
         <v>4078</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B205" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="1">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A206">
         <v>4079</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B206" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="1">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A207">
         <v>4080</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B207" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" s="1">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A208">
         <v>4081</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B208" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" s="1">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A209">
         <v>4082</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B209" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" s="1">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>4083</v>
+      </c>
+      <c r="B210" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A211">
         <v>4084</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B211" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" s="1">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>4085</v>
+      </c>
+      <c r="B212" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A213">
         <v>4086</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B213" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" s="1">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A214">
         <v>4087</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B214" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" s="1">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A215">
         <v>4088</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B215" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" s="1">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>4089</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A219">
         <v>4092</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B219" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" s="1">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A220">
         <v>4093</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B220" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" s="1">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A221">
         <v>4094</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B221" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" s="1">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A222">
         <v>4095</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B222" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" s="1">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A223">
         <v>4096</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B223" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" s="1">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A224">
         <v>4097</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B224" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" s="1">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A225">
         <v>4098</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B225" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" s="1">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A226">
         <v>4099</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B226" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" s="1">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A227">
         <v>4100</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B227" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" s="1">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A228">
         <v>4101</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B228" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" s="1">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>4102</v>
+      </c>
+      <c r="B229" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>4103</v>
+      </c>
+      <c r="B230" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>4104</v>
+      </c>
+      <c r="B231" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <v>4105</v>
+      </c>
+      <c r="B232" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A233">
+        <v>4106</v>
+      </c>
+      <c r="B233" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A234">
         <v>4107</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B234" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" s="1">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A235">
         <v>4108</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B235" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" s="1">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A236">
         <v>4109</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B236" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" s="1">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A237">
         <v>4110</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B237" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" s="1">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A238">
         <v>4111</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B238" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" s="1">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A239">
         <v>4112</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B239" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" s="1">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A240">
         <v>4113</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B240" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" s="1">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A241">
         <v>4114</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B241" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" s="1">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A242">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A243">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A244">
         <v>4117</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B244" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" s="1">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A245">
+        <v>4118</v>
+      </c>
+      <c r="B245" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A246">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A247">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A248">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A249">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A250">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A251">
         <v>4126</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B251" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A160" s="1">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A252">
+        <v>4128</v>
+      </c>
+      <c r="B252" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A253">
+        <v>4129</v>
+      </c>
+      <c r="B253" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A254">
         <v>4130</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B254" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" s="1">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A255">
         <v>4132</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B255" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" s="1">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A257">
         <v>4135</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B257" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" s="1">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A258">
         <v>4136</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B258" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A164" s="1">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A259">
         <v>4137</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B259" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" s="1">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A260">
         <v>4138</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B260" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A166" s="1">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A261">
         <v>4139</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B261" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A167" s="1">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A262">
         <v>4140</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B262" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A168" s="1">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A263">
         <v>4141</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B263" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A169" s="1">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A264">
         <v>4142</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B264" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A170" s="1">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A265">
         <v>4143</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B265" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A171" s="1">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A266">
         <v>4144</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B266" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A172" s="1">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A267">
+        <v>4145</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A268">
         <v>4146</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B268" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A173" s="1">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A269">
         <v>4147</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B269" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A174" s="1">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A270">
         <v>4148</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B270" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A175" s="1">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A271">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A272">
         <v>4150</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B272" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A176" s="1">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A273">
         <v>4151</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B273" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A177" s="1">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A274">
         <v>4152</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B274" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A178" s="1">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A275">
         <v>4153</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B275" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A179" s="1">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A276">
+        <v>4154</v>
+      </c>
+      <c r="B276" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A277">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A278">
         <v>4156</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B278" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A180" s="1">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A279">
+        <v>4157</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A280">
         <v>4158</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B280" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A181" s="1">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A281">
         <v>4159</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B281" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A182" s="1">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A282">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A283">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A284">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A285">
         <v>4163</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B285" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A183" s="1">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A286">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A287">
         <v>4165</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B287" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A184" s="1">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A288">
+        <v>4166</v>
+      </c>
+      <c r="B288" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A289">
+        <v>4167</v>
+      </c>
+      <c r="B289" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A290">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A291">
         <v>4169</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B291" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A185" s="1">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A292">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A293">
         <v>4171</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B293" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A186" s="1">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A294">
         <v>4172</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B294" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A187" s="1">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A295">
         <v>4173</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B295" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A188" s="1">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A296">
         <v>4174</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B296" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A189" s="1">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A297">
         <v>4175</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B297" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A190" s="1">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A298">
         <v>4176</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B298" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A191" s="1">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A299">
         <v>4177</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B299" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A192" s="1">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A300">
         <v>4178</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B300" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A193" s="1">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A301">
         <v>4179</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B301" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A194" s="1">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A302">
         <v>4180</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B302" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A195" s="1">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A303">
         <v>4181</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B303" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A196" s="1">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A304">
         <v>4182</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B304" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A197" s="1">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A305">
         <v>4183</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B305" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A198" s="1">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A306">
         <v>4185</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B306" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A199" s="1">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A307">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A308">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A309">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A310">
+        <v>4190</v>
+      </c>
+      <c r="B310" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A311">
+        <v>4191</v>
+      </c>
+      <c r="B311" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A312">
         <v>4192</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B312" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A200" s="1">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A313">
         <v>4193</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B313" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A201" s="1">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A314">
         <v>4194</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B314" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A202" s="1">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A315">
         <v>4195</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B315" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A203" s="1">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A316">
         <v>4197</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B316" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A204" s="1">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A317">
         <v>4198</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B317" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A205" s="1">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A318">
         <v>4199</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B318" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A206" s="1">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A319">
         <v>4200</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B319" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A207" s="1">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A320">
         <v>4201</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B320" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A208" s="1">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A321">
         <v>4202</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B321" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A209" s="1">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A322">
         <v>4205</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B322" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A210" s="1">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A323">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A324">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A325">
+        <v>4209</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A326">
         <v>4212</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B326" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A211" s="1">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A327">
         <v>4213</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B327" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A212" s="1">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A328">
         <v>4214</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B328" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A213" s="1">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A329">
         <v>4216</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B329" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A214" s="1">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A330">
+        <v>4217</v>
+      </c>
+      <c r="B330" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A331">
+        <v>4218</v>
+      </c>
+      <c r="B331" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A332">
+        <v>4219</v>
+      </c>
+      <c r="B332" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A333">
+        <v>4220</v>
+      </c>
+      <c r="B333" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A334">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A335">
+        <v>4222</v>
+      </c>
+      <c r="B335" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A336">
+        <v>4223</v>
+      </c>
+      <c r="B336" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A337">
+        <v>4224</v>
+      </c>
+      <c r="B337" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A338">
+        <v>4225</v>
+      </c>
+      <c r="B338" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A339">
+        <v>4226</v>
+      </c>
+      <c r="B339" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A340">
+        <v>4227</v>
+      </c>
+      <c r="B340" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A341">
+        <v>4228</v>
+      </c>
+      <c r="B341" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A342">
+        <v>4229</v>
+      </c>
+      <c r="B342" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A343">
+        <v>4230</v>
+      </c>
+      <c r="B343" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A344">
+        <v>4231</v>
+      </c>
+      <c r="B344" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A345">
+        <v>4232</v>
+      </c>
+      <c r="B345" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A346">
+        <v>4233</v>
+      </c>
+      <c r="B346" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A347">
+        <v>4234</v>
+      </c>
+      <c r="B347" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A348">
+        <v>4235</v>
+      </c>
+      <c r="B348" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A349">
         <v>4236</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B349" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A215" s="1">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A350">
+        <v>4237</v>
+      </c>
+      <c r="B350" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A351">
+        <v>4238</v>
+      </c>
+      <c r="B351" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A352">
         <v>4239</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B352" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A216" s="1">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A353">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A354">
+        <v>4241</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A355">
+        <v>4242</v>
+      </c>
+      <c r="B355" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A356">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A357">
         <v>4247</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B357" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A217" s="1">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A358">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A359">
         <v>4249</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B359" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A218" s="1">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A360">
         <v>4250</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B360" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A219" s="1">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A361">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A362">
         <v>4252</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B362" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A220" s="1">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A363">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A364">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A365">
         <v>4255</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B365" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A221" s="1">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A366">
         <v>4257</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B366" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A222" s="1">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A367">
         <v>4258</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B367" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A223" s="1">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A368">
         <v>4259</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B368" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A224" s="1">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A369">
         <v>4260</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B369" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A225" s="1">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A370">
         <v>4261</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B370" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A226" s="1">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A371">
         <v>4262</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B371" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A227" s="1">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A372">
         <v>4263</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B372" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A228" s="1">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A373">
         <v>4264</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B373" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A229" s="1">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A374">
         <v>4265</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B374" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A230" s="1">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A375">
         <v>4266</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B375" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A231" s="1">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A376">
         <v>4267</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B376" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A232" s="1">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A377">
         <v>4268</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B377" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A233" s="1">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A378">
         <v>4272</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B378" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A234" s="1">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A379">
         <v>4274</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B379" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A235" s="1">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A380">
+        <v>4276</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A381">
         <v>4278</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B381" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A236" s="1">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A382">
+        <v>4281</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A383">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A384">
         <v>4283</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B384" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A237" s="1">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A385">
         <v>4284</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B385" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A238" s="1">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A386">
+        <v>4285</v>
+      </c>
+      <c r="B386" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A387">
+        <v>4286</v>
+      </c>
+      <c r="B387" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A388">
+        <v>4287</v>
+      </c>
+      <c r="B388" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A389">
+        <v>4288</v>
+      </c>
+      <c r="B389" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A390">
         <v>4289</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B390" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A239" s="1">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A391">
         <v>4290</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B391" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A240" s="1">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A392">
         <v>4291</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B392" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A241" s="1">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A393">
         <v>4292</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B393" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A242" s="1">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A394">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A395">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A396">
         <v>4295</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B396" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A243" s="1">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A397">
         <v>4296</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B397" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A244" s="1">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A398">
         <v>4297</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B398" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A245" s="1">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A399">
         <v>4298</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B399" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A246" s="1">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A400">
+        <v>4299</v>
+      </c>
+      <c r="B400" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A401">
         <v>4300</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B401" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A247" s="1">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A402">
         <v>4301</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B402" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A248" s="1">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A403">
+        <v>4302</v>
+      </c>
+      <c r="B403" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A404">
+        <v>4303</v>
+      </c>
+      <c r="B404" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A405">
         <v>4304</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B405" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A249" s="1">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A406">
         <v>4305</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B406" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A250" s="1">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A407">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A408">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A409">
         <v>4309</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B409" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A251" s="1">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A410">
         <v>4310</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B410" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A252" s="1">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A411">
         <v>4311</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B411" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A253" s="1">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A412">
         <v>4312</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B412" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A254" s="1">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A413">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A414">
         <v>4314</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B414" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A255" s="1">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A415">
         <v>4315</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B415" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A256" s="1">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A416">
         <v>4316</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B416" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A257" s="1">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A417">
         <v>4317</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B417" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A258" s="1">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A418">
+        <v>4318</v>
+      </c>
+      <c r="B418" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A419">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A420">
         <v>4320</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B420" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A259" s="1">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A421">
         <v>4321</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B421" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A260" s="1">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A422">
         <v>4322</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B422" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A261" s="1">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A423">
         <v>4323</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B423" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A262" s="1">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A424">
+        <v>4324</v>
+      </c>
+      <c r="B424" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A425">
         <v>4325</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B425" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A263" s="1">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A426">
+        <v>4326</v>
+      </c>
+      <c r="B426" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A427">
+        <v>4327</v>
+      </c>
+      <c r="B427" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A428">
         <v>4328</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B428" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A264" s="1">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A429">
         <v>4329</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B429" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A265" s="1">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A430">
         <v>4330</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B430" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A266" s="1">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A431">
         <v>4331</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B431" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A267" s="1">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A432">
         <v>4332</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B432" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A268" s="1">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A433">
         <v>4333</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B433" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A269" s="1">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A434">
         <v>4334</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B434" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A270" s="1">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A435">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A436">
         <v>4336</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B436" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A271" s="1">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A437">
         <v>4337</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B437" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A272" s="1">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A438">
         <v>4338</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B438" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A273" s="1">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A439">
         <v>4339</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B439" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A274" s="1">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A440">
         <v>4340</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B440" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A275" s="1">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A441">
+        <v>4341</v>
+      </c>
+      <c r="B441" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A442">
+        <v>4342</v>
+      </c>
+      <c r="B442" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A443">
         <v>4343</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B443" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A276" s="1">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A444">
         <v>4344</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B444" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A277" s="1">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A445">
         <v>4345</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B445" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A278" s="1">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A446">
+        <v>4346</v>
+      </c>
+      <c r="B446" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A447">
         <v>4347</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B447" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A279" s="1">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A448">
         <v>4348</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B448" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A280" s="1">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A449">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A450">
         <v>4350</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B450" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A281" s="1">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A451">
         <v>4351</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B451" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A282" s="1">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A452">
         <v>4352</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B452" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A283" s="1">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A453">
         <v>4353</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B453" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A284" s="1">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A454">
+        <v>4354</v>
+      </c>
+      <c r="B454" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A455">
         <v>4355</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B455" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A285" s="1">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A456">
         <v>4356</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B456" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A286" s="1">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A457">
         <v>4357</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B457" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A287" s="1">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A458">
         <v>4358</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B458" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A288" s="1">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A459">
         <v>4359</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B459" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A289" s="1">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A460">
         <v>4360</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B460" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A290" s="1">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A461">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A462">
         <v>4362</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B462" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A291" s="1">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A463">
         <v>4363</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B463" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A292" s="1">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A464">
         <v>4364</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B464" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A293" s="1">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A465">
+        <v>4365</v>
+      </c>
+      <c r="B465" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A466">
         <v>4366</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B466" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A294" s="1">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A467">
         <v>4367</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B467" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A295" s="1">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A468">
+        <v>4368</v>
+      </c>
+      <c r="B468" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A469">
         <v>4385</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B469" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A296" s="1">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A470">
         <v>4386</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B470" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A297" s="1">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A471">
         <v>4387</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B471" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A298" s="1">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A472">
         <v>4389</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B472" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A299" s="1">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A473">
         <v>4390</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B473" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A300" s="1">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A474">
+        <v>4397</v>
+      </c>
+      <c r="B474" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A475">
         <v>4398</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B475" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A301" s="1">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A476">
         <v>5378</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B476" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A302" s="1">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A477">
+        <v>5379</v>
+      </c>
+      <c r="B477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A478">
+        <v>5501</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A479">
+        <v>5763</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A480">
         <v>5764</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B480" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A303" s="1">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A481">
         <v>5765</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B481" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A304" s="1">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A482">
+        <v>5766</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A483">
+        <v>5767</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A484">
         <v>5768</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B484" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A305" s="1">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A485">
+        <v>5769</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A486">
+        <v>5770</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A487">
         <v>5771</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B487" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A306" s="1">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A488">
+        <v>5837</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A489">
         <v>5838</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B489" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A307" s="1">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A490">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A491">
         <v>5906</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B491" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A308" s="1">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A492">
         <v>5907</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B492" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A309" s="1">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A493">
         <v>5909</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B493" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A310" s="1">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A494">
         <v>5910</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B494" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A311" s="1">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A495">
         <v>5911</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B495" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A312" s="1">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A496">
         <v>5912</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B496" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A313" s="1">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A497">
+        <v>5913</v>
+      </c>
+      <c r="B497" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A498">
         <v>5914</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B498" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A314" s="1">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A499">
         <v>5915</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B499" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A315" s="1">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A500">
+        <v>5975</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A501">
         <v>5976</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B501" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A316" s="1">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A502">
         <v>5977</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B502" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A317" s="1">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A503">
+        <v>5978</v>
+      </c>
+      <c r="B503" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A504">
         <v>5979</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B504" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A318" s="1">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A505">
         <v>5980</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B505" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A319" s="1">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A506">
         <v>5981</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B506" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A320" s="1">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A507">
         <v>5982</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B507" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A321" s="1">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A508">
         <v>5983</v>
       </c>
-      <c r="B321" t="s">
+      <c r="B508" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A322" s="1">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A509">
         <v>5984</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B509" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A323" s="1">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A510">
         <v>5985</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B510" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A324" s="1">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A511">
         <v>5986</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B511" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A325" s="1">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A512">
         <v>5987</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B512" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A326" s="1">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A513">
         <v>5988</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B513" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A327" s="1">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A514">
+        <v>5989</v>
+      </c>
+      <c r="B514" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A515">
+        <v>5990</v>
+      </c>
+      <c r="B515" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A516">
+        <v>5991</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A517">
         <v>6001</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B517" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A328" s="1">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A518">
         <v>6002</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B518" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A329" s="1">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A519">
         <v>6003</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B519" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A330" s="1">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A520">
         <v>6004</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B520" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A331" s="1">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A521">
         <v>6005</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B521" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A332" s="1">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A522">
+        <v>6006</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A523">
+        <v>6007</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A524">
+        <v>6008</v>
+      </c>
+      <c r="B524" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A525">
+        <v>6009</v>
+      </c>
+      <c r="B525" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A526">
+        <v>6011</v>
+      </c>
+      <c r="B526" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A527">
+        <v>6012</v>
+      </c>
+      <c r="B527" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A528">
+        <v>6013</v>
+      </c>
+      <c r="B528" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A529">
+        <v>6014</v>
+      </c>
+      <c r="B529" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A530">
+        <v>6015</v>
+      </c>
+      <c r="B530" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A531">
+        <v>6016</v>
+      </c>
+      <c r="B531" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A532">
+        <v>6017</v>
+      </c>
+      <c r="B532" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A533">
+        <v>6018</v>
+      </c>
+      <c r="B533" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A534">
+        <v>6019</v>
+      </c>
+      <c r="B534" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A535">
+        <v>6020</v>
+      </c>
+      <c r="B535" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A536">
+        <v>6021</v>
+      </c>
+      <c r="B536" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A537">
+        <v>6022</v>
+      </c>
+      <c r="B537" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A538">
+        <v>6023</v>
+      </c>
+      <c r="B538" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A539">
+        <v>6024</v>
+      </c>
+      <c r="B539" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A540">
+        <v>6025</v>
+      </c>
+      <c r="B540" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A541">
+        <v>6026</v>
+      </c>
+      <c r="B541" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A542">
+        <v>6027</v>
+      </c>
+      <c r="B542" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A543">
+        <v>6028</v>
+      </c>
+      <c r="B543" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A544">
+        <v>6029</v>
+      </c>
+      <c r="B544" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A545">
+        <v>6030</v>
+      </c>
+      <c r="B545" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A546">
+        <v>6031</v>
+      </c>
+      <c r="B546" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A547">
+        <v>6032</v>
+      </c>
+      <c r="B547" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A548">
+        <v>6033</v>
+      </c>
+      <c r="B548" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A549">
+        <v>6034</v>
+      </c>
+      <c r="B549" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A550">
+        <v>6035</v>
+      </c>
+      <c r="B550" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A551">
+        <v>6036</v>
+      </c>
+      <c r="B551" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A552">
+        <v>6037</v>
+      </c>
+      <c r="B552" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A553">
+        <v>6038</v>
+      </c>
+      <c r="B553" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A554">
+        <v>6039</v>
+      </c>
+      <c r="B554" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A555">
+        <v>6040</v>
+      </c>
+      <c r="B555" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A556">
+        <v>6041</v>
+      </c>
+      <c r="B556" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A557">
+        <v>6042</v>
+      </c>
+      <c r="B557" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A558">
+        <v>6043</v>
+      </c>
+      <c r="B558" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A559">
+        <v>6044</v>
+      </c>
+      <c r="B559" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A560">
+        <v>6045</v>
+      </c>
+      <c r="B560" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A561">
+        <v>6046</v>
+      </c>
+      <c r="B561" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A562">
+        <v>6047</v>
+      </c>
+      <c r="B562" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A563">
+        <v>6048</v>
+      </c>
+      <c r="B563" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A564">
+        <v>6049</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A565">
+        <v>6050</v>
+      </c>
+      <c r="B565" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A566">
         <v>6051</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B566" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A333" s="1">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A567">
+        <v>6052</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A568">
         <v>6053</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B568" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A334" s="1">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A569">
         <v>6054</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B569" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A335" s="1">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A570">
         <v>6055</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B570" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A336" s="1">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A571">
         <v>6160</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B571" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A337" s="1">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A572">
         <v>6161</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B572" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A338" s="1">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A573">
         <v>6162</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B573" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A339" s="1">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A574">
         <v>6163</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B574" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A340" s="1">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A575">
         <v>6164</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B575" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A341" s="1">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A576">
         <v>6165</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B576" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A342" s="1">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A577">
         <v>6167</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B577" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A343" s="1">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A578">
+        <v>6168</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A579">
         <v>6169</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B579" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A344" s="1">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A580">
+        <v>6170</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A581">
+        <v>6171</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A582">
         <v>6172</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B582" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A345" s="1">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A583">
         <v>6173</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B583" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A346" s="1">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A584">
+        <v>6174</v>
+      </c>
+      <c r="B584" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A585">
+        <v>6176</v>
+      </c>
+      <c r="B585" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A586">
+        <v>6177</v>
+      </c>
+      <c r="B586" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A587">
+        <v>6178</v>
+      </c>
+      <c r="B587" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A588">
+        <v>6179</v>
+      </c>
+      <c r="B588" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A589">
+        <v>6180</v>
+      </c>
+      <c r="B589" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A590">
+        <v>6181</v>
+      </c>
+      <c r="B590" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A591">
+        <v>6182</v>
+      </c>
+      <c r="B591" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A592">
+        <v>6183</v>
+      </c>
+      <c r="B592" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A593">
+        <v>6184</v>
+      </c>
+      <c r="B593" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A594">
+        <v>6185</v>
+      </c>
+      <c r="B594" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A595">
+        <v>6186</v>
+      </c>
+      <c r="B595" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A596">
+        <v>6187</v>
+      </c>
+      <c r="B596" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A597">
+        <v>6188</v>
+      </c>
+      <c r="B597" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A598">
+        <v>6189</v>
+      </c>
+      <c r="B598" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A599">
+        <v>6190</v>
+      </c>
+      <c r="B599" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A600">
+        <v>6191</v>
+      </c>
+      <c r="B600" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A601">
         <v>6204</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B601" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A347" s="1">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A602">
         <v>6205</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B602" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A348" s="1">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A603">
+        <v>6209</v>
+      </c>
+      <c r="B603" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A604">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A605">
+        <v>6211</v>
+      </c>
+      <c r="B605" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A606">
+        <v>6212</v>
+      </c>
+      <c r="B606" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A607">
+        <v>6213</v>
+      </c>
+      <c r="B607" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A608">
+        <v>6214</v>
+      </c>
+      <c r="B608" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A609">
+        <v>6215</v>
+      </c>
+      <c r="B609" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A610">
         <v>6263</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B610" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A349" s="1">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A611">
         <v>6264</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B611" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A350" s="1">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A612">
         <v>6265</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B612" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A351" s="1">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A613">
         <v>6266</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B613" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A352" s="1">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A614">
         <v>7250</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B614" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A353" s="1">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A615">
         <v>7252</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B615" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A354" s="1">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A616">
+        <v>7253</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A617">
+        <v>7254</v>
+      </c>
+      <c r="B617" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A618">
         <v>7256</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B618" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A355" s="1">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A619">
         <v>7257</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B619" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A356" s="1">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A620">
         <v>7258</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B620" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A357" s="1">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A621">
+        <v>7265</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A622">
+        <v>9093</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A623">
         <v>9422</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B623" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A358" s="1">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A624">
         <v>9423</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B624" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A359" s="1">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A625">
         <v>10207</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B625" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A360" s="1">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A626">
         <v>10208</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B626" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A361" s="1">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A627">
         <v>10209</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B627" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A362" s="1">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A628">
         <v>10210</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B628" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A363" s="1">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A629">
         <v>10211</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B629" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A364" s="1">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A630">
+        <v>10212</v>
+      </c>
+      <c r="B630" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A631">
+        <v>10213</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A632">
+        <v>10214</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A633">
+        <v>10215</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A634">
         <v>10216</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B634" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A365" s="1">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A635">
         <v>10217</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B635" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A366" s="1">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A636">
         <v>10220</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B636" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A367" s="1">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A637">
         <v>10229</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B637" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A368" s="1">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A638">
+        <v>10230</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A639">
         <v>10233</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B639" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A369" s="1">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A640">
+        <v>10234</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A641">
+        <v>10235</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A642">
+        <v>10236</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A643">
+        <v>10237</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A644">
         <v>10238</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B644" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A370" s="1">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A645">
         <v>10239</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B645" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A371" s="1">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A646">
         <v>10240</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B646" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A372" s="1">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A647">
         <v>10241</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B647" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A373" s="1">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A648">
         <v>10242</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B648" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A374" s="1">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A649">
         <v>10243</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B649" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A375" s="1">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A650">
         <v>10244</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B650" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A376" s="1">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A651">
         <v>10245</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B651" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A377" s="1">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A652">
         <v>10247</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B652" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A378" s="1">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A653">
         <v>10248</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B653" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A379" s="1">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A654">
         <v>10249</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B654" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A380" s="1">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A655">
+        <v>10250</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A656">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A657">
+        <v>10252</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A658">
         <v>10253</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B658" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A381" s="1">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A659">
         <v>10254</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B659" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A382" s="1">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A660">
         <v>10255</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B660" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A383" s="1">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A661">
         <v>10256</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B661" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A384" s="1">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A662">
         <v>10257</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B662" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A385" s="1">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A663">
         <v>10263</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B663" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A386" s="1">
-        <v>10414</v>
-      </c>
-      <c r="B386" t="s">
-        <v>383</v>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A664">
+        <v>10738</v>
       </c>
     </row>
   </sheetData>

--- a/Mapas/Excels/Nodes_ENTSOE.xlsx
+++ b/Mapas/Excels/Nodes_ENTSOE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8F97EF-47D5-4893-B1F3-08A8A6A1BD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2300C6CC-01C4-43CD-892E-08256B7695CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3ECAB5B8-515A-4E5B-A53D-CF71BE525F88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="592">
   <si>
     <t>ALDEADAVILA II</t>
   </si>
@@ -1686,6 +1686,132 @@
   </si>
   <si>
     <t>VALDECARRETAS</t>
+  </si>
+  <si>
+    <t>CRISTOBAL COLON</t>
+  </si>
+  <si>
+    <t>TORREARENILLAS</t>
+  </si>
+  <si>
+    <t>ALJARAFE</t>
+  </si>
+  <si>
+    <t>ONUBA</t>
+  </si>
+  <si>
+    <t>SIDEGASA</t>
+  </si>
+  <si>
+    <t>PIEROLA</t>
+  </si>
+  <si>
+    <t>PEÑAFLOR</t>
+  </si>
+  <si>
+    <t>MONTETORRERO</t>
+  </si>
+  <si>
+    <t>MANGRANERS</t>
+  </si>
+  <si>
+    <t>MONTBLANC</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>LOS VIENTOS</t>
+  </si>
+  <si>
+    <t>L.VISO</t>
+  </si>
+  <si>
+    <t>ENCE</t>
+  </si>
+  <si>
+    <t>EL ESPARTAL</t>
+  </si>
+  <si>
+    <t>PALOS</t>
+  </si>
+  <si>
+    <t>FUENDETODOS</t>
+  </si>
+  <si>
+    <t>MEDINACELI</t>
+  </si>
+  <si>
+    <t>EL VENTERO</t>
+  </si>
+  <si>
+    <t>TERRER</t>
+  </si>
+  <si>
+    <t>RUEDA DE JALON</t>
+  </si>
+  <si>
+    <t>EL OLIVAR</t>
+  </si>
+  <si>
+    <t>AVE ZARAGOZA</t>
+  </si>
+  <si>
+    <t>TORRES DEL SEGRE</t>
+  </si>
+  <si>
+    <t>LA ESPLUGA</t>
+  </si>
+  <si>
+    <t>COSTALUZ</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>ALBATARREC</t>
+  </si>
+  <si>
+    <t>ALCARRAS</t>
+  </si>
+  <si>
+    <t>PUEBLA DE GUZMAN</t>
+  </si>
+  <si>
+    <t>BELCHITE</t>
+  </si>
+  <si>
+    <t>CABEZO DE SAN ROQUE</t>
+  </si>
+  <si>
+    <t>JALON</t>
+  </si>
+  <si>
+    <t>CAN BARBA</t>
+  </si>
+  <si>
+    <t>MAS FIGUERAS</t>
+  </si>
+  <si>
+    <t>CARIÑENA</t>
+  </si>
+  <si>
+    <t>JUNEDA</t>
+  </si>
+  <si>
+    <t>TRASONA</t>
+  </si>
+  <si>
+    <t>CHUCENA</t>
+  </si>
+  <si>
+    <t>CARTUJOS</t>
+  </si>
+  <si>
+    <t>PUIGPERLAT</t>
+  </si>
+  <si>
+    <t>SIERRA COSTERA</t>
   </si>
 </sst>
 </file>
@@ -2210,11 +2336,17 @@
       <c r="A22">
         <v>3894</v>
       </c>
+      <c r="B22" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>3895</v>
       </c>
+      <c r="B23" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -2252,6 +2384,9 @@
       <c r="A28">
         <v>3900</v>
       </c>
+      <c r="B28" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
@@ -2281,6 +2416,9 @@
       <c r="A32">
         <v>3904</v>
       </c>
+      <c r="B32" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
@@ -2752,6 +2890,9 @@
       <c r="A92">
         <v>3965</v>
       </c>
+      <c r="B92" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
@@ -3084,6 +3225,9 @@
       <c r="A135">
         <v>4008</v>
       </c>
+      <c r="B135" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136">
@@ -3105,14 +3249,14 @@
       <c r="A138">
         <v>4011</v>
       </c>
-      <c r="B138" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>4012</v>
       </c>
+      <c r="B139" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140">
@@ -3421,6 +3565,9 @@
       <c r="A179">
         <v>4052</v>
       </c>
+      <c r="B179" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180">
@@ -3495,6 +3642,9 @@
       <c r="A189">
         <v>4062</v>
       </c>
+      <c r="B189" t="s">
+        <v>557</v>
+      </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190">
@@ -3715,6 +3865,9 @@
       <c r="A218">
         <v>4091</v>
       </c>
+      <c r="B218" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219">
@@ -3930,6 +4083,9 @@
       <c r="A246">
         <v>4120</v>
       </c>
+      <c r="B246" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247">
@@ -3940,16 +4096,25 @@
       <c r="A248">
         <v>4123</v>
       </c>
+      <c r="B248" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>4124</v>
       </c>
+      <c r="B249" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>4125</v>
       </c>
+      <c r="B250" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251">
@@ -4080,6 +4245,9 @@
       <c r="A267">
         <v>4145</v>
       </c>
+      <c r="B267" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268">
@@ -4109,6 +4277,9 @@
       <c r="A271">
         <v>4149</v>
       </c>
+      <c r="B271" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272">
@@ -4154,6 +4325,9 @@
       <c r="A277">
         <v>4155</v>
       </c>
+      <c r="B277" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278">
@@ -4188,16 +4362,25 @@
       <c r="A282">
         <v>4160</v>
       </c>
+      <c r="B282" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>4161</v>
       </c>
+      <c r="B283" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>4162</v>
       </c>
+      <c r="B284" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285">
@@ -4370,11 +4553,17 @@
       <c r="A307">
         <v>4186</v>
       </c>
+      <c r="B307" t="s">
+        <v>569</v>
+      </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>4187</v>
       </c>
+      <c r="B308" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309">
@@ -4717,11 +4906,17 @@
       <c r="A353">
         <v>4240</v>
       </c>
+      <c r="B353" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>4241</v>
       </c>
+      <c r="B354" t="s">
+        <v>572</v>
+      </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355">
@@ -5015,11 +5210,17 @@
       <c r="A394">
         <v>4293</v>
       </c>
+      <c r="B394" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>4294</v>
       </c>
+      <c r="B395" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396">
@@ -5113,11 +5314,17 @@
       <c r="A407">
         <v>4307</v>
       </c>
+      <c r="B407" t="s">
+        <v>575</v>
+      </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>4308</v>
       </c>
+      <c r="B408" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409">
@@ -5155,6 +5362,9 @@
       <c r="A413">
         <v>4313</v>
       </c>
+      <c r="B413" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414">
@@ -5200,6 +5410,9 @@
       <c r="A419">
         <v>4319</v>
       </c>
+      <c r="B419" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420">
@@ -5317,14 +5530,14 @@
       <c r="A434">
         <v>4334</v>
       </c>
-      <c r="B434" t="s">
-        <v>266</v>
-      </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>4335</v>
       </c>
+      <c r="B435" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436">
@@ -5434,6 +5647,9 @@
       <c r="A449">
         <v>4349</v>
       </c>
+      <c r="B449" t="s">
+        <v>579</v>
+      </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450">
@@ -5735,6 +5951,9 @@
       <c r="A490">
         <v>5905</v>
       </c>
+      <c r="B490" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491">
@@ -5982,11 +6201,17 @@
       <c r="A522">
         <v>6006</v>
       </c>
+      <c r="B522" t="s">
+        <v>581</v>
+      </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523">
         <v>6007</v>
       </c>
+      <c r="B523" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524">
@@ -6333,6 +6558,9 @@
       <c r="A567">
         <v>6052</v>
       </c>
+      <c r="B567" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568">
@@ -6418,6 +6646,9 @@
       <c r="A578">
         <v>6168</v>
       </c>
+      <c r="B578" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579">
@@ -6821,6 +7052,9 @@
       <c r="A631">
         <v>10213</v>
       </c>
+      <c r="B631" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632">
@@ -6868,6 +7102,9 @@
       <c r="A638">
         <v>10230</v>
       </c>
+      <c r="B638" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639">
@@ -6881,11 +7118,17 @@
       <c r="A640">
         <v>10234</v>
       </c>
+      <c r="B640" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641">
         <v>10235</v>
       </c>
+      <c r="B641" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642">
@@ -6989,6 +7232,9 @@
       <c r="A655">
         <v>10250</v>
       </c>
+      <c r="B655" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656">
@@ -6999,6 +7245,9 @@
       <c r="A657">
         <v>10252</v>
       </c>
+      <c r="B657" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658">
@@ -7051,6 +7300,9 @@
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664">
         <v>10738</v>
+      </c>
+      <c r="B664" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/Mapas/Excels/Nodes_ENTSOE.xlsx
+++ b/Mapas/Excels/Nodes_ENTSOE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2300C6CC-01C4-43CD-892E-08256B7695CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBA09C2-AA7C-42E8-836E-857ED8B1C74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3ECAB5B8-515A-4E5B-A53D-CF71BE525F88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="615">
   <si>
     <t>ALDEADAVILA II</t>
   </si>
@@ -1812,6 +1812,75 @@
   </si>
   <si>
     <t>SIERRA COSTERA</t>
+  </si>
+  <si>
+    <t>SAN ROQUE</t>
+  </si>
+  <si>
+    <t>VALDECABALLEROS</t>
+  </si>
+  <si>
+    <t>COMPOSTILLA I</t>
+  </si>
+  <si>
+    <t>ALMAZAN</t>
+  </si>
+  <si>
+    <t>SANGÜESA</t>
+  </si>
+  <si>
+    <t>MONZON</t>
+  </si>
+  <si>
+    <t>EL PALMERAL</t>
+  </si>
+  <si>
+    <t>PEÑALBA</t>
+  </si>
+  <si>
+    <t>VIRTUS</t>
+  </si>
+  <si>
+    <t>COMPOSTILLA II</t>
+  </si>
+  <si>
+    <t>CINCA</t>
+  </si>
+  <si>
+    <t>MUNIESA</t>
+  </si>
+  <si>
+    <t>SIDERURGICA</t>
+  </si>
+  <si>
+    <t>ALCORES</t>
+  </si>
+  <si>
+    <t>SANTA MARIA DE GRADO</t>
+  </si>
+  <si>
+    <t>UNINSA</t>
+  </si>
+  <si>
+    <t>ALBAL</t>
+  </si>
+  <si>
+    <t>PARQUE CENTRAL</t>
+  </si>
+  <si>
+    <t>CIUDAD RODRIGO</t>
+  </si>
+  <si>
+    <t>CAÑAVERAL</t>
+  </si>
+  <si>
+    <t>CASAQUEMADA</t>
+  </si>
+  <si>
+    <t>SANTA ELVIRA</t>
+  </si>
+  <si>
+    <t>TORRELLANO</t>
   </si>
 </sst>
 </file>
@@ -2488,6 +2557,9 @@
       <c r="A41">
         <v>3913</v>
       </c>
+      <c r="B41" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
@@ -2589,6 +2661,9 @@
       <c r="A54">
         <v>3926</v>
       </c>
+      <c r="B54" t="s">
+        <v>593</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
@@ -2786,9 +2861,6 @@
       <c r="A79">
         <v>3952</v>
       </c>
-      <c r="B79" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
@@ -3098,6 +3170,9 @@
       <c r="A118">
         <v>3991</v>
       </c>
+      <c r="B118" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119">
@@ -3141,13 +3216,16 @@
         <v>3997</v>
       </c>
       <c r="B124" t="s">
-        <v>69</v>
+        <v>594</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>3998</v>
       </c>
+      <c r="B125" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126">
@@ -3249,6 +3327,9 @@
       <c r="A138">
         <v>4011</v>
       </c>
+      <c r="B138" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139">
@@ -3581,6 +3662,9 @@
       <c r="A181">
         <v>4054</v>
       </c>
+      <c r="B181" t="s">
+        <v>595</v>
+      </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182">
@@ -3674,6 +3758,9 @@
       <c r="A193">
         <v>4066</v>
       </c>
+      <c r="B193" t="s">
+        <v>596</v>
+      </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194">
@@ -3855,11 +3942,17 @@
       <c r="A216">
         <v>4089</v>
       </c>
+      <c r="B216" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>4090</v>
       </c>
+      <c r="B217" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218">
@@ -4152,14 +4245,14 @@
       <c r="A255">
         <v>4132</v>
       </c>
-      <c r="B255" t="s">
-        <v>158</v>
-      </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>4133</v>
       </c>
+      <c r="B256" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257">
@@ -4341,6 +4434,9 @@
       <c r="A279">
         <v>4157</v>
       </c>
+      <c r="B279" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280">
@@ -4394,6 +4490,9 @@
       <c r="A286">
         <v>4164</v>
       </c>
+      <c r="B286" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287">
@@ -4436,6 +4535,9 @@
       <c r="A292">
         <v>4170</v>
       </c>
+      <c r="B292" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293">
@@ -4688,6 +4790,9 @@
       <c r="A325">
         <v>4209</v>
       </c>
+      <c r="B325" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326">
@@ -4930,6 +5035,9 @@
       <c r="A356">
         <v>4243</v>
       </c>
+      <c r="B356" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357">
@@ -4982,6 +5090,9 @@
       <c r="A364">
         <v>4254</v>
       </c>
+      <c r="B364" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365">
@@ -5120,11 +5231,17 @@
       <c r="A382">
         <v>4281</v>
       </c>
+      <c r="B382" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>4282</v>
       </c>
+      <c r="B383" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384">
@@ -5227,7 +5344,7 @@
         <v>4295</v>
       </c>
       <c r="B396" t="s">
-        <v>239</v>
+        <v>606</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
@@ -5530,6 +5647,9 @@
       <c r="A434">
         <v>4334</v>
       </c>
+      <c r="B434" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435">
@@ -5743,6 +5863,9 @@
       <c r="A461">
         <v>4361</v>
       </c>
+      <c r="B461" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462">
@@ -6156,6 +6279,9 @@
       <c r="A516">
         <v>5991</v>
       </c>
+      <c r="B516" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517">
@@ -6840,14 +6966,14 @@
       <c r="A603">
         <v>6209</v>
       </c>
-      <c r="B603" t="s">
-        <v>542</v>
-      </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604">
         <v>6210</v>
       </c>
+      <c r="B604" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605">
@@ -7060,11 +7186,17 @@
       <c r="A632">
         <v>10214</v>
       </c>
+      <c r="B632" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633">
         <v>10215</v>
       </c>
+      <c r="B633" t="s">
+        <v>611</v>
+      </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634">
@@ -7134,11 +7266,17 @@
       <c r="A642">
         <v>10236</v>
       </c>
+      <c r="B642" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643">
         <v>10237</v>
       </c>
+      <c r="B643" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644">
@@ -7239,6 +7377,9 @@
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656">
         <v>10251</v>
+      </c>
+      <c r="B656" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">

--- a/Mapas/Excels/Nodes_ENTSOE.xlsx
+++ b/Mapas/Excels/Nodes_ENTSOE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBA09C2-AA7C-42E8-836E-857ED8B1C74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F4BBDC-A8CF-42BA-B13D-94CCCDF20E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3ECAB5B8-515A-4E5B-A53D-CF71BE525F88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="625">
   <si>
     <t>ALDEADAVILA II</t>
   </si>
@@ -1881,6 +1881,36 @@
   </si>
   <si>
     <t>TORRELLANO</t>
+  </si>
+  <si>
+    <t>SANTIAGO DE COMPOSTELA</t>
+  </si>
+  <si>
+    <t>SAN VICENTE</t>
+  </si>
+  <si>
+    <t>ABOÑO</t>
+  </si>
+  <si>
+    <t>LUBIAN</t>
+  </si>
+  <si>
+    <t>VILLAMECA</t>
+  </si>
+  <si>
+    <t>ALDEADAVILA</t>
+  </si>
+  <si>
+    <t>LUDRIO</t>
+  </si>
+  <si>
+    <t>MEDIODIA</t>
+  </si>
+  <si>
+    <t>CEUTA</t>
+  </si>
+  <si>
+    <t>CALABOSC</t>
   </si>
 </sst>
 </file>
@@ -2861,6 +2891,9 @@
       <c r="A79">
         <v>3952</v>
       </c>
+      <c r="B79" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
@@ -3202,6 +3235,9 @@
       <c r="A122">
         <v>3995</v>
       </c>
+      <c r="B122" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123">
@@ -3484,6 +3520,9 @@
       <c r="A158">
         <v>4031</v>
       </c>
+      <c r="B158" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159">
@@ -4245,6 +4284,9 @@
       <c r="A255">
         <v>4132</v>
       </c>
+      <c r="B255" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256">
@@ -4522,6 +4564,9 @@
       <c r="A290">
         <v>4168</v>
       </c>
+      <c r="B290" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291">
@@ -4616,7 +4661,7 @@
         <v>4180</v>
       </c>
       <c r="B302" t="s">
-        <v>191</v>
+        <v>619</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -5999,6 +6044,9 @@
       <c r="A478">
         <v>5501</v>
       </c>
+      <c r="B478" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479">
@@ -6154,6 +6202,9 @@
       <c r="A500">
         <v>5975</v>
       </c>
+      <c r="B500" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501">
@@ -6663,6 +6714,9 @@
       <c r="A564">
         <v>6049</v>
       </c>
+      <c r="B564" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565">
@@ -7067,6 +7121,9 @@
       <c r="A616">
         <v>7253</v>
       </c>
+      <c r="B616" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617">
@@ -7103,6 +7160,9 @@
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621">
         <v>7265</v>
+      </c>
+      <c r="B621" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
